--- a/etl/datos_limpios.xlsx
+++ b/etl/datos_limpios.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>difficulty_level</t>
+          <t>duration_level</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>para la masa:, 3 tazas de harina, 70 grs de manteca derretida, 1 taza de leche tibia, 1 cucharadita de polvos de hornear, 1 cucharadita de sal, para el pino, 2 a 3 cucharadas de aceite maravilla o canola, 2 cebollas picadas en cuadros, 1/2 kilo de surtido de mariscos, 1 cucharadita de ají color (puede reemplazar por paprika), 1 cucharadita de ají en pasta, 1/2 cucharadita de orégano, sal a gusto</t>
+          <t>Para la masa:, 3 tazas de harina, 70 grs de manteca derretida, 1 taza de leche tibia, 1 cucharadita de polvos de hornear, 1 cucharadita de sal, para el pino, 2 a 3 cucharadas de aceite maravilla o canola, 2 cebollas picadas en cuadros, 1/2 kilo de surtido de mariscos, 1 cucharadita de ají color (puede reemplazar por paprika), 1 cucharadita de ají en pasta, 1/2 cucharadita de orégano, sal a gusto</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nan</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nan</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">

--- a/etl/datos_limpios.xlsx
+++ b/etl/datos_limpios.xlsx
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>53.69875222816399</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>26.24777183600713</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="4">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>28.5204991087344</v>
+        <v>28.52</v>
       </c>
     </row>
     <row r="5">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>53.87700534759358</v>
+        <v>53.88</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>33.06595365418895</v>
+        <v>33.07</v>
       </c>
     </row>
     <row r="7">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>39.88413547237077</v>
+        <v>39.88</v>
       </c>
     </row>
     <row r="8">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>53.52049910873441</v>
+        <v>53.52</v>
       </c>
     </row>
     <row r="9">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>75.57932263814618</v>
+        <v>75.58</v>
       </c>
     </row>
     <row r="10">
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>27.31729055258467</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="11">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>51.42602495543672</v>
+        <v>51.43</v>
       </c>
     </row>
     <row r="12">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>44.4295900178253</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>43.31550802139037</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="14">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>27.98573975044564</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="15">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>23.44028520499108</v>
+        <v>23.44</v>
       </c>
     </row>
     <row r="16">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>67.8698752228164</v>
+        <v>67.87</v>
       </c>
     </row>
     <row r="17">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>39.88413547237077</v>
+        <v>39.88</v>
       </c>
     </row>
     <row r="18">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Para la masa:, 3 tazas de harina, 70 grs de manteca derretida, 1 taza de leche tibia, 1 cucharadita de polvos de hornear, 1 cucharadita de sal, para el pino, 2 a 3 cucharadas de aceite maravilla o canola, 2 cebollas picadas en cuadros, 1/2 kilo de surtido de mariscos, 1 cucharadita de ají color (puede reemplazar por paprika), 1 cucharadita de ají en pasta, 1/2 cucharadita de orégano, sal a gusto</t>
+          <t>para la masa:, 3 tazas de harina, 70 grs de manteca derretida, 1 taza de leche tibia, 1 cucharadita de polvos de hornear, 1 cucharadita de sal, para el pino, 2 a 3 cucharadas de aceite maravilla o canola, 2 cebollas picadas en cuadros, 1/2 kilo de surtido de mariscos, 1 cucharadita de ají color (puede reemplazar por paprika), 1 cucharadita de ají en pasta, 1/2 cucharadita de orégano, sal a gusto</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>48.97504456327985</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="19">
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>60.87344028520499</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="20">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>29.50089126559715</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="21">
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>13.99286987522282</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="22">
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>50.57932263814617</v>
+        <v>50.58</v>
       </c>
     </row>
     <row r="23">
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>42.15686274509804</v>
+        <v>42.16</v>
       </c>
     </row>
     <row r="24">
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>35.51693404634581</v>
+        <v>35.52</v>
       </c>
     </row>
     <row r="25">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>28.5204991087344</v>
+        <v>28.52</v>
       </c>
     </row>
     <row r="26">
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>30.25846702317291</v>
+        <v>30.26</v>
       </c>
     </row>
     <row r="27">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>73.1283422459893</v>
+        <v>73.13</v>
       </c>
     </row>
     <row r="28">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>45.14260249554367</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="29">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>72.9500891265597</v>
+        <v>72.95</v>
       </c>
     </row>
     <row r="30">
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>49.68805704099822</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="31">
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>54.76827094474153</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="32">
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>28.5204991087344</v>
+        <v>28.52</v>
       </c>
     </row>
     <row r="33">
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>27.80748663101605</v>
+        <v>27.81</v>
       </c>
     </row>
     <row r="34">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>38.14616755793226</v>
+        <v>38.15</v>
       </c>
     </row>
     <row r="35">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>48.97504456327985</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="36">
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>37.61140819964349</v>
+        <v>37.61</v>
       </c>
     </row>
     <row r="37">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>25.53475935828877</v>
+        <v>25.53</v>
       </c>
     </row>
     <row r="38">
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>25.71301247771836</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="39">
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>33.06595365418895</v>
+        <v>33.07</v>
       </c>
     </row>
     <row r="40">
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>28.5204991087344</v>
+        <v>28.52</v>
       </c>
     </row>
     <row r="41">
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>75.75757575757575</v>
+        <v>75.76000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>41.04278074866311</v>
+        <v>41.04</v>
       </c>
     </row>
     <row r="43">
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>21.3458110516934</v>
+        <v>21.35</v>
       </c>
     </row>
     <row r="44">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>71.21212121212122</v>
+        <v>71.20999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>27.62923351158645</v>
+        <v>27.63</v>
       </c>
     </row>
     <row r="47">
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>44.4295900178253</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="48">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>43.98395721925134</v>
+        <v>43.98</v>
       </c>
     </row>
     <row r="49">
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>51.60427807486631</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="50">
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>9.269162210338681</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="51">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>48.97504456327985</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="52">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>44.96434937611409</v>
+        <v>44.96</v>
       </c>
     </row>
     <row r="53">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>39.03743315508022</v>
+        <v>39.04</v>
       </c>
     </row>
     <row r="54">
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>44.6078431372549</v>
+        <v>44.61</v>
       </c>
     </row>
     <row r="55">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>20.63279857397504</v>
+        <v>20.63</v>
       </c>
     </row>
     <row r="56">
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>21.70231729055259</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="57">
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>33.06595365418895</v>
+        <v>33.07</v>
       </c>
     </row>
     <row r="58">
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>35.33868092691623</v>
+        <v>35.34</v>
       </c>
     </row>
     <row r="59">
@@ -2780,7 +2780,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>30.79322638146167</v>
+        <v>30.79</v>
       </c>
     </row>
     <row r="60">
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>42.15686274509804</v>
+        <v>42.16</v>
       </c>
     </row>
     <row r="61">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>53.87700534759358</v>
+        <v>53.88</v>
       </c>
     </row>
     <row r="62">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>19.42959001782531</v>
+        <v>19.43</v>
       </c>
     </row>
     <row r="63">
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>23.61853832442068</v>
+        <v>23.62</v>
       </c>
     </row>
     <row r="64">
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>37.61140819964349</v>
+        <v>37.61</v>
       </c>
     </row>
     <row r="65">
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>39.88413547237077</v>
+        <v>39.88</v>
       </c>
     </row>
     <row r="66">
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>48.97504456327985</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="67">
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>26.24777183600713</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="68">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>28.16399286987522</v>
+        <v>28.16</v>
       </c>
     </row>
     <row r="69">
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>20.81105169340464</v>
+        <v>20.81</v>
       </c>
     </row>
   </sheetData>

--- a/etl/datos_limpios.xlsx
+++ b/etl/datos_limpios.xlsx
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>53.7</v>
+        <v>53.69875222816399</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>26.25</v>
+        <v>26.24777183600713</v>
       </c>
     </row>
     <row r="4">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>28.52</v>
+        <v>28.5204991087344</v>
       </c>
     </row>
     <row r="5">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>53.88</v>
+        <v>53.87700534759358</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>33.07</v>
+        <v>33.06595365418895</v>
       </c>
     </row>
     <row r="7">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>39.88</v>
+        <v>39.88413547237077</v>
       </c>
     </row>
     <row r="8">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>53.52</v>
+        <v>53.52049910873441</v>
       </c>
     </row>
     <row r="9">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>75.58</v>
+        <v>75.57932263814618</v>
       </c>
     </row>
     <row r="10">
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>27.32</v>
+        <v>27.31729055258467</v>
       </c>
     </row>
     <row r="11">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>51.43</v>
+        <v>51.42602495543672</v>
       </c>
     </row>
     <row r="12">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>44.43</v>
+        <v>44.4295900178253</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>43.32</v>
+        <v>43.31550802139037</v>
       </c>
     </row>
     <row r="14">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>27.99</v>
+        <v>27.98573975044564</v>
       </c>
     </row>
     <row r="15">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>23.44</v>
+        <v>23.44028520499108</v>
       </c>
     </row>
     <row r="16">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>67.87</v>
+        <v>67.8698752228164</v>
       </c>
     </row>
     <row r="17">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>39.88</v>
+        <v>39.88413547237077</v>
       </c>
     </row>
     <row r="18">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>48.98</v>
+        <v>48.97504456327985</v>
       </c>
     </row>
     <row r="19">
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>60.87</v>
+        <v>60.87344028520499</v>
       </c>
     </row>
     <row r="20">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>29.5</v>
+        <v>29.50089126559715</v>
       </c>
     </row>
     <row r="21">
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>13.99</v>
+        <v>13.99286987522282</v>
       </c>
     </row>
     <row r="22">
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>50.58</v>
+        <v>50.57932263814617</v>
       </c>
     </row>
     <row r="23">
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>42.16</v>
+        <v>42.15686274509804</v>
       </c>
     </row>
     <row r="24">
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>35.52</v>
+        <v>35.51693404634581</v>
       </c>
     </row>
     <row r="25">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>28.52</v>
+        <v>28.5204991087344</v>
       </c>
     </row>
     <row r="26">
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>30.26</v>
+        <v>30.25846702317291</v>
       </c>
     </row>
     <row r="27">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>73.13</v>
+        <v>73.1283422459893</v>
       </c>
     </row>
     <row r="28">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>45.14</v>
+        <v>45.14260249554367</v>
       </c>
     </row>
     <row r="29">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>72.95</v>
+        <v>72.9500891265597</v>
       </c>
     </row>
     <row r="30">
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>49.69</v>
+        <v>49.68805704099822</v>
       </c>
     </row>
     <row r="31">
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>54.77</v>
+        <v>54.76827094474153</v>
       </c>
     </row>
     <row r="32">
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>28.52</v>
+        <v>28.5204991087344</v>
       </c>
     </row>
     <row r="33">
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>27.81</v>
+        <v>27.80748663101605</v>
       </c>
     </row>
     <row r="34">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>38.15</v>
+        <v>38.14616755793226</v>
       </c>
     </row>
     <row r="35">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>48.98</v>
+        <v>48.97504456327985</v>
       </c>
     </row>
     <row r="36">
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>37.61</v>
+        <v>37.61140819964349</v>
       </c>
     </row>
     <row r="37">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>25.53</v>
+        <v>25.53475935828877</v>
       </c>
     </row>
     <row r="38">
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>25.71</v>
+        <v>25.71301247771836</v>
       </c>
     </row>
     <row r="39">
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>33.07</v>
+        <v>33.06595365418895</v>
       </c>
     </row>
     <row r="40">
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>28.52</v>
+        <v>28.5204991087344</v>
       </c>
     </row>
     <row r="41">
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>75.76000000000001</v>
+        <v>75.75757575757575</v>
       </c>
     </row>
     <row r="42">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>41.04</v>
+        <v>41.04278074866311</v>
       </c>
     </row>
     <row r="43">
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>21.35</v>
+        <v>21.3458110516934</v>
       </c>
     </row>
     <row r="44">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>71.20999999999999</v>
+        <v>71.21212121212122</v>
       </c>
     </row>
     <row r="46">
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>27.63</v>
+        <v>27.62923351158645</v>
       </c>
     </row>
     <row r="47">
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>44.43</v>
+        <v>44.4295900178253</v>
       </c>
     </row>
     <row r="48">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>43.98</v>
+        <v>43.98395721925134</v>
       </c>
     </row>
     <row r="49">
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>51.6</v>
+        <v>51.60427807486631</v>
       </c>
     </row>
     <row r="50">
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>9.27</v>
+        <v>9.269162210338681</v>
       </c>
     </row>
     <row r="51">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>48.98</v>
+        <v>48.97504456327985</v>
       </c>
     </row>
     <row r="52">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>44.96</v>
+        <v>44.96434937611409</v>
       </c>
     </row>
     <row r="53">
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>39.04</v>
+        <v>39.03743315508022</v>
       </c>
     </row>
     <row r="54">
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>44.61</v>
+        <v>44.6078431372549</v>
       </c>
     </row>
     <row r="55">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>20.63</v>
+        <v>20.63279857397504</v>
       </c>
     </row>
     <row r="56">
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>21.7</v>
+        <v>21.70231729055259</v>
       </c>
     </row>
     <row r="57">
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>33.07</v>
+        <v>33.06595365418895</v>
       </c>
     </row>
     <row r="58">
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>35.34</v>
+        <v>35.33868092691623</v>
       </c>
     </row>
     <row r="59">
@@ -2780,7 +2780,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>30.79</v>
+        <v>30.79322638146167</v>
       </c>
     </row>
     <row r="60">
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>42.16</v>
+        <v>42.15686274509804</v>
       </c>
     </row>
     <row r="61">
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>53.88</v>
+        <v>53.87700534759358</v>
       </c>
     </row>
     <row r="62">
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>19.43</v>
+        <v>19.42959001782531</v>
       </c>
     </row>
     <row r="63">
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>23.62</v>
+        <v>23.61853832442068</v>
       </c>
     </row>
     <row r="64">
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>37.61</v>
+        <v>37.61140819964349</v>
       </c>
     </row>
     <row r="65">
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>39.88</v>
+        <v>39.88413547237077</v>
       </c>
     </row>
     <row r="66">
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>48.98</v>
+        <v>48.97504456327985</v>
       </c>
     </row>
     <row r="67">
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>26.25</v>
+        <v>26.24777183600713</v>
       </c>
     </row>
     <row r="68">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>28.16</v>
+        <v>28.16399286987522</v>
       </c>
     </row>
     <row r="69">
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>20.81</v>
+        <v>20.81105169340464</v>
       </c>
     </row>
   </sheetData>
